--- a/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 25,58</t>
+          <t>-7,71; 26,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 31,54</t>
+          <t>1,88; 30,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,45; -1,98</t>
+          <t>-40,98; -1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 21,29</t>
+          <t>-5,17; 20,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 360,53</t>
+          <t>-40,1; 375,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 1085,21</t>
+          <t>-14,14; 1198,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,25</t>
+          <t>-100,0; 29,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 7,78</t>
+          <t>-12,9; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 1,13</t>
+          <t>-23,63; 0,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 14,29</t>
+          <t>-9,36; 13,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 5,95</t>
+          <t>-15,97; 5,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 144,82</t>
+          <t>-78,58; 159,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 49,43</t>
+          <t>-87,61; 23,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 248,73</t>
+          <t>-60,05; 260,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,53; 89,83</t>
+          <t>-82,4; 88,02</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 3,91</t>
+          <t>-21,4; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 17,43</t>
+          <t>-8,6; 16,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,44</t>
+          <t>-13,69; 9,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 7,33</t>
+          <t>-17,64; 7,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,99; 61,12</t>
+          <t>-90,11; 88,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 350,01</t>
+          <t>-61,96; 397,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,36; 117,18</t>
+          <t>-86,26; 107,41</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 18,38</t>
+          <t>-17,5; 16,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 2,92</t>
+          <t>-18,41; 3,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 29,66</t>
+          <t>-6,13; 26,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 12,32</t>
+          <t>-8,0; 12,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 136,59</t>
+          <t>-62,08; 120,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,05; 48,97</t>
+          <t>-89,02; 51,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 427,82</t>
+          <t>-36,66; 388,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 7,03</t>
+          <t>-7,48; 6,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 5,91</t>
+          <t>-6,68; 6,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 6,46</t>
+          <t>-8,45; 7,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 3,64</t>
+          <t>-8,19; 3,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 55,85</t>
+          <t>-38,72; 53,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,57; 62,87</t>
+          <t>-42,51; 62,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 55,84</t>
+          <t>-43,91; 70,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 50,59</t>
+          <t>-62,8; 52,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 26,94</t>
+          <t>-8,42; 25,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 30,75</t>
+          <t>0,31; 30,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,98; -1,56</t>
+          <t>-41,16; -2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 20,76</t>
+          <t>-4,44; 22,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,1; 375,5</t>
+          <t>-39,27; 365,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 1198,95</t>
+          <t>-13,13; 1142,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,53</t>
+          <t>-100,0; 31,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 8,02</t>
+          <t>-12,83; 9,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 0,47</t>
+          <t>-23,08; 1,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 13,32</t>
+          <t>-8,82; 12,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 5,48</t>
+          <t>-17,37; 5,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,58; 159,72</t>
+          <t>-76,0; 272,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,61; 23,08</t>
+          <t>-90,07; 24,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 260,14</t>
+          <t>-57,13; 207,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 88,02</t>
+          <t>-83,31; 84,76</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 5,09</t>
+          <t>-22,1; 3,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 16,8</t>
+          <t>-7,17; 18,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 9,42</t>
+          <t>-13,53; 9,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 7,45</t>
+          <t>-16,83; 6,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-90,11; 88,41</t>
+          <t>-100,0; 65,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,96; 397,94</t>
+          <t>-58,99; 390,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 5386844,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,26; 107,41</t>
+          <t>-85,01; 104,96</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 16,89</t>
+          <t>-17,42; 17,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,41; 3,32</t>
+          <t>-17,58; 4,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 26,47</t>
+          <t>-6,09; 29,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 12,56</t>
+          <t>-8,1; 11,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 120,92</t>
+          <t>-61,61; 135,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,02; 51,22</t>
+          <t>-89,27; 81,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 388,48</t>
+          <t>-33,64; 476,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 6,89</t>
+          <t>-7,32; 7,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,09</t>
+          <t>-6,75; 5,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 7,19</t>
+          <t>-8,06; 5,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,95</t>
+          <t>-7,72; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 53,68</t>
+          <t>-38,46; 55,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 62,47</t>
+          <t>-42,07; 60,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 70,67</t>
+          <t>-44,31; 55,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 52,54</t>
+          <t>-58,5; 51,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumieron medicamentos para la alergia</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,86</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>135,02%</t>
+          <t>128,17%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 25,58</t>
+          <t>-8,01; 25,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 30,52</t>
+          <t>0,87; 31,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -2,79</t>
+          <t>-41,45; -1,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 22,22</t>
+          <t>-4,38; 22,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 365,24</t>
+          <t>-38,18; 360,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 1142,77</t>
+          <t>-11,93; 1085,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,7</t>
+          <t>-100,0; 21,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,43</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-39,22%</t>
+          <t>-24,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 9,42</t>
+          <t>-13,08; 7,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 1,55</t>
+          <t>-23,65; 1,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 12,33</t>
+          <t>-8,53; 14,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 5,05</t>
+          <t>-14,42; 9,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 272,7</t>
+          <t>-76,97; 144,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 24,82</t>
+          <t>-87,63; 49,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 207,85</t>
+          <t>-57,72; 248,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,31; 84,76</t>
+          <t>-79,04; 134,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-30,41%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 3,12</t>
+          <t>-21,47; 3,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 18,76</t>
+          <t>-6,8; 17,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 9,08</t>
+          <t>-12,79; 10,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 6,7</t>
+          <t>-11,25; 12,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 65,23</t>
+          <t>-90,99; 61,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,99; 390,92</t>
+          <t>-58,84; 350,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 5386844,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-85,01; 104,96</t>
+          <t>-65,74; 230,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 17,56</t>
+          <t>-17,36; 18,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 4,0</t>
+          <t>-19,41; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 29,28</t>
+          <t>-6,57; 29,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 11,87</t>
+          <t>-7,08; 13,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,61; 135,78</t>
+          <t>-64,12; 136,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 81,76</t>
+          <t>-90,05; 48,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,64; 476,86</t>
+          <t>-37,74; 427,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 7,08</t>
+          <t>-7,67; 7,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,7</t>
+          <t>-6,53; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,69</t>
+          <t>-8,12; 6,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 3,87</t>
+          <t>-6,03; 6,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 55,48</t>
+          <t>-37,86; 55,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 60,27</t>
+          <t>-42,57; 62,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 55,02</t>
+          <t>-46,22; 55,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,5; 51,23</t>
+          <t>-46,01; 89,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A08-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14,77</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-21,61</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,86</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>185,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-74,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>128,17%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.041756505759873</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.357312804097025</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.390467377862614</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.607814245011069</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.039108150683304</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1.897929962602697</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.7178537111243385</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>1.535303639459348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,01; 25,58</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 31,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-41,45; -1,98</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 22,19</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-38,18; 360,53</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-11,93; 1085,21</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 21,25</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.9204336216142531</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.1763980797824186</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.774546457095054</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.8863250608983917</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2876472801665547</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2829122539479463</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.321609475643569</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.952282022579857</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.07121046486528523</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.302945361544662</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4.923349301510969</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>12.42882629514257</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.789733248262626</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-10,45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,34</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-56,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-24,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; 7,78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-23,65; 1,13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,53; 14,29</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-14,42; 9,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-76,97; 144,82</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-87,63; 49,43</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-57,72; 248,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-79,04; 134,41</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1499787300783435</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.730220746738314</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6951355840885086</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.248649407789298</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.06912237369328897</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5220424589800524</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3346588683981003</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3763190016090046</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-9,2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,34</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-55,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-14,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.2666054532185</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.256973870885489</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.598559604909042</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.903812099052301</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7460852638669259</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8697361583385774</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.6428520862397755</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.8637641257478562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-21,47; 3,91</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,8; 17,43</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-12,79; 10,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-11,25; 12,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-90,99; 61,12</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,84; 350,01</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-65,74; 230,06</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.18961923382746</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.5933336700258975</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.303284943297934</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.332349505438909</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>2.583906336935891</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.8608909276718292</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>3.408990599012893</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.8492153451869148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +815,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-7,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10,42</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-51,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.548392246439455</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8767405385231346</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.1199607912571803</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.425370381733512</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.6507459276259387</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.4250804723435015</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.09031930531841248</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1162608076829125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,36; 18,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-19,41; 2,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,57; 29,66</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,08; 13,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-64,12; 136,59</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-90,05; 48,97</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-37,74; 427,82</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.827586176266413</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.680689606083266</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.188460295664627</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.486402409498672</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6033230271089158</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6539583326472466</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1700689031939561</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.818745019550783</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.956980663874293</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.324540265990131</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3315851389322089</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>5.91154584720528</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>67691.24607424556</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.242559908295492</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.561495583077786</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.800608799963987</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.816532347499179</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.2303863562870918</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3833169138557835</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5761574476283347</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.8479893976491052</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2223733250166124</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.25169144835547</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.714764078484616</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.9511228317747197</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.509658860653339</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.7999286658427786</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9386727172322578</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.426146151098396</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.370425271747296</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4471783846332376</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.111409628447444</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.3708288409843</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.7026149346550465</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5651715703790975</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4.939393615257536</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-4,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-6,73%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-7,67; 7,03</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,53; 5,91</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,12; 6,46</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,03; 6,56</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-37,86; 55,85</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-42,57; 62,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-46,22; 55,84</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-46,01; 89,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.395708881312417</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1697209045577849</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04844959860439597</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.02731939975422308</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1221573719578321</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.06362321552146143</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.01974695493197374</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.01119811055061635</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.816572512265673</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.567397481053771</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.457243137778523</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.559840166163025</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4719669554203281</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4701069592103087</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4452118627030113</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.487800810091196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.260808955026806</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.240097342562043</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.545906819941361</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.609333746894324</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.511812201717574</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.6891210814525509</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.878297629535423</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.9580522599839997</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1109,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
